--- a/public/templates/prices_template.xlsx
+++ b/public/templates/prices_template.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="prices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contracts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,22 +28,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,11 +49,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,64 +416,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Contract Number</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Part Number</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Date From</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Date To</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Quantity From</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Quantity To</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Lot Price</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
     </row>
@@ -522,6 +518,11 @@
       <c r="H2" t="n">
         <v>8.5</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -558,6 +559,11 @@
       <c r="H3" t="n">
         <v>6.5</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -594,6 +600,11 @@
       <c r="H4" t="n">
         <v>4.5</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -630,6 +641,11 @@
       <c r="H5" t="n">
         <v>2.5</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -666,6 +682,11 @@
       <c r="I6" t="n">
         <v>1000</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -675,68 +696,78 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CD500</t>
+          <t>XR-900</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Globex Corp</t>
+          <t>Globex GmbH</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-06-30</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>9999999</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>12.75</v>
+        <v>12.4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CT-2026-003</t>
+          <t>CT-2026-002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EF800</t>
+          <t>XR-900</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Initech Ltd</t>
+          <t>Globex GmbH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-06-30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>9999999</v>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -747,7 +778,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EF800</t>
+          <t>KP-77</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -757,7 +788,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -766,34 +797,39 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>200</v>
-      </c>
-      <c r="H9" t="n">
-        <v>12</v>
+        <v>9999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4500</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CT-2026-003</t>
+          <t>CT-2026-004</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EF800</t>
+          <t>NP-50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Initech Ltd</t>
+          <t>NorPlas SA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -802,13 +838,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>9999999</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>9.5</v>
+        <v>15</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -819,104 +860,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GH900</t>
+          <t>NP-50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Umbrella Co</t>
+          <t>NorPlas SA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="G11" t="n">
         <v>9999999</v>
       </c>
-      <c r="I11" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CT-2026-005</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IJ100</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Stark Supplies</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>100</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CT-2026-005</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>IJ100</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Stark Supplies</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>101</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.1</v>
+      <c r="H11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -933,29 +907,29 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>username</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -974,7 +948,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Administrador</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -996,7 +970,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Usuário Padrão</t>
+          <t>Standard User</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1004,6 +978,194 @@
           <t>user</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Contract Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CT-2026-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Acme master agreement</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CT-2026-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Globex EU framework</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CT-2026-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Initech UK lot supply</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CT-2026-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NorPlas BR resale</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
